--- a/src/attributions/attributions_ig_traj_482.xlsx
+++ b/src/attributions/attributions_ig_traj_482.xlsx
@@ -1568,46 +1568,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.02412956706708274</v>
+        <v>0.02636679170491706</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1100023018228785</v>
+        <v>0.03657060532297129</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.06701394379777625</v>
+        <v>-0.03896745993178077</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.07585604196834457</v>
+        <v>0.1045762378212729</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001223293218876386</v>
+        <v>0.0002471329126097788</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01394149303317151</v>
+        <v>0.006082971991879444</v>
       </c>
       <c r="O3" t="n">
         <v>-0</v>
@@ -1619,22 +1619,22 @@
         <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1051138551042382</v>
+        <v>-0.04083940163093613</v>
       </c>
       <c r="T3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.06843901536279097</v>
+        <v>0.02286500560061496</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.04373647978503293</v>
+        <v>-0.05314706144286326</v>
       </c>
       <c r="X3" t="n">
         <v>-0</v>
@@ -1646,136 +1646,136 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.567091501209941e-11</v>
+        <v>4.705839656232457e-11</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0035888832268991</v>
+        <v>-0.01051171839087696</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.04214415784733924</v>
+        <v>-0.006610617342705489</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.001952431755144169</v>
+        <v>0.01006713716508768</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.05921370582215233</v>
+        <v>-0.03948117463840425</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.1421953892829898</v>
+        <v>-0.1211528085779393</v>
       </c>
       <c r="AP3" t="n">
         <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
         <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.05310492416699602</v>
+        <v>-0.110953152024483</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.379544954835725</v>
+        <v>0.04205254838485795</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.3324474995540729</v>
+        <v>-0.1849607574316446</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
         <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.03458804470747524</v>
+        <v>0.01456136991506491</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE3" t="n">
-        <v>-3.41176476007202e-11</v>
+        <v>1.069466931523769e-11</v>
       </c>
       <c r="BF3" t="n">
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.005007881624580197</v>
+        <v>-0.007322248177501038</v>
       </c>
       <c r="BH3" t="n">
         <v>-0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
         <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.02781554265313806</v>
+        <v>0.03999006393253914</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.05242782315946877</v>
+        <v>-0.006691987094237612</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.3086303913918834</v>
+        <v>0.06163460003006758</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
@@ -1784,19 +1784,19 @@
         <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.0514446690026354</v>
+        <v>-0.1207315544108803</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.2463180990534939</v>
+        <v>0.09242576502393929</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.08282616473895538</v>
+        <v>-0.1039782672976465</v>
       </c>
       <c r="BZ3" t="n">
         <v>-0</v>
@@ -1811,22 +1811,22 @@
         <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.06606472891869268</v>
+        <v>0.06042378267165269</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.05533081075350106</v>
+        <v>-0.02152051914331654</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.1137879585676979</v>
+        <v>0.08414147889482627</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ3" t="n">
         <v>0</v>
@@ -1835,55 +1835,55 @@
         <v>-0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>-0.008469534763698381</v>
+        <v>0.005417315106236878</v>
       </c>
       <c r="CN3" t="n">
         <v>-0</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.125396508616477</v>
+        <v>-0.01574864287287924</v>
       </c>
       <c r="CP3" t="n">
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.3085995970575179</v>
+        <v>-0.05353634714559427</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS3" t="n">
         <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
         <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.09097968261779532</v>
+        <v>0.05552294154629663</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.03613207697488765</v>
+        <v>-0.0322313575648573</v>
       </c>
       <c r="CY3" t="n">
         <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.06759860226137845</v>
+        <v>0.04664626254203826</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
@@ -1892,49 +1892,49 @@
         <v>-0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.007293737477747855</v>
+        <v>0.03887162067443811</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0.001211701485568644</v>
+        <v>0.0007301406130031577</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.1453386387515229</v>
+        <v>0.1415279518813485</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL3" t="n">
         <v>-0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.05619818882019745</v>
+        <v>0.05600150590503591</v>
       </c>
       <c r="DO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.05648599129684293</v>
+        <v>0.02095797820566156</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.3999088640952327</v>
+        <v>-0.07253801393014044</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
         <v>0</v>
@@ -1943,52 +1943,52 @@
         <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.04750449881000075</v>
+        <v>0.001911707415591632</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.01689444369774915</v>
+        <v>0.08930002066487515</v>
       </c>
       <c r="DZ3" t="n">
         <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.0613000842130934</v>
+        <v>-0.06723297786436842</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.05373606077760216</v>
+        <v>0.03961643500605572</v>
       </c>
       <c r="EG3" t="n">
         <v>0</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.09664346358345439</v>
+        <v>0.002423560771397427</v>
       </c>
       <c r="EI3" t="n">
         <v>-0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0600444370747244</v>
+        <v>0.07085058443362277</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
         <v>0</v>
@@ -1997,52 +1997,52 @@
         <v>0</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>-0.03744218926757437</v>
+        <v>0.01101628067669809</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.07337321720685119</v>
+        <v>0.005049572403804692</v>
       </c>
       <c r="ER3" t="n">
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.05608000488160763</v>
+        <v>0.07939798052971365</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.06368545788733319</v>
+        <v>0.06260484347598136</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0.04375169993516087</v>
+        <v>-0.03660690793709083</v>
       </c>
       <c r="FA3" t="n">
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.04026822468264317</v>
+        <v>0.05538145765344325</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD3" t="n">
         <v>0</v>
@@ -2051,49 +2051,49 @@
         <v>-0</v>
       </c>
       <c r="FF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.06763275060125137</v>
+        <v>0.1693458892773538</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.008234146832062219</v>
+        <v>-0.01303491124737668</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.03746866809136035</v>
+        <v>0.05036699678924159</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
         <v>-0</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO3" t="n">
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.03406047802194283</v>
+        <v>0.1357007179798935</v>
       </c>
       <c r="FQ3" t="n">
         <v>-0</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.00247252953390392</v>
+        <v>0.001059731382174904</v>
       </c>
       <c r="FS3" t="n">
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.01034566410363313</v>
+        <v>0.006697973413127075</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
@@ -2108,31 +2108,31 @@
         <v>0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.03136528862342676</v>
+        <v>0.09545099526204341</v>
       </c>
       <c r="FZ3" t="n">
         <v>-0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.03795695150210573</v>
+        <v>-0.002883102522056079</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -2140,133 +2140,133 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1211819157664879</v>
+        <v>0.05682268811882025</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-4.134245893944926e-11</v>
+        <v>-2.795496242306671e-11</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.01063648287731348</v>
+        <v>-0.009537574136660266</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03358105386299076</v>
+        <v>0.02097680680864106</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07241061724624952</v>
+        <v>0.05147986588401347</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0002149640379912181</v>
+        <v>-0.0001481212546597813</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1085944678530057</v>
+        <v>0.03389520622095525</v>
       </c>
       <c r="U4" t="n">
         <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0195808948514246</v>
+        <v>-0.02144753253427509</v>
       </c>
       <c r="W4" t="n">
-        <v>0.08648268021851931</v>
+        <v>-0.01302438278354386</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.005294840023630678</v>
+        <v>-0.002912489105658037</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0005053323858199621</v>
+        <v>-0.003689828109928999</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.002152505539785458</v>
+        <v>-0.007446074175497465</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.03759862431620133</v>
+        <v>0.05896455891906975</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.04299322225323698</v>
+        <v>-0.009669109030126515</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.004724930499492922</v>
+        <v>0.03132828251473351</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -2275,25 +2275,25 @@
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.308015788227169</v>
+        <v>0.1479484164330881</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.01044622533063445</v>
+        <v>-0.02708481891056217</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1730805006043288</v>
+        <v>-0.05513338960332372</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
         <v>-0</v>
@@ -2302,16 +2302,16 @@
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.0001648048900989459</v>
+        <v>-0.001968830641333058</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.006226723273378641</v>
+        <v>-0.001298121446642956</v>
       </c>
       <c r="BG4" t="n">
-        <v>-3.855690585880787e-11</v>
+        <v>-1.217439433686884e-11</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
@@ -2320,7 +2320,7 @@
         <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
         <v>-0</v>
       </c>
       <c r="BM4" t="n">
-        <v>-0.02860302559308479</v>
+        <v>-0.002153881344106413</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.09362087626853847</v>
+        <v>0.01025338532848217</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.02818177574891659</v>
+        <v>0.02982769926419166</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2356,25 +2356,25 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.1747124880764446</v>
+        <v>0.1127888288292221</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.01362292619600245</v>
+        <v>-0.02926522245879925</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.03093305060064313</v>
+        <v>-0.002724165481764412</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
         <v>0</v>
@@ -2383,46 +2383,46 @@
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.07351281324309408</v>
+        <v>-0.05003082110253637</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.003582457360319491</v>
+        <v>0.03494991457470942</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.01280617777303103</v>
+        <v>0.003880887542409112</v>
       </c>
       <c r="CI4" t="n">
         <v>-0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.009577179359625744</v>
+        <v>-0.03283303840844146</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.07433067836003375</v>
+        <v>0.03953159611228305</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.1374251016355245</v>
+        <v>0.03372311059528794</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
@@ -2434,52 +2434,52 @@
         <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.06594957234184227</v>
+        <v>-0.0523779779345135</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.03287966040704467</v>
+        <v>0.03876902956029234</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.007001078309340069</v>
+        <v>0.006539473998108252</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.06001344569550355</v>
+        <v>-0.02097432336162812</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.0006844198442234736</v>
+        <v>-0.00420213622829705</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0.0002226306445577741</v>
+        <v>0.0004854178204407909</v>
       </c>
       <c r="DJ4" t="n">
         <v>-0</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
         <v>0</v>
@@ -2491,25 +2491,25 @@
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.07319488144773806</v>
+        <v>-0.02084324403416303</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.05159249347737672</v>
+        <v>0.006525766915933265</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.02503694290217342</v>
+        <v>-0.02822313701480304</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
@@ -2518,151 +2518,151 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.05005004460498483</v>
+        <v>0.03625552117650729</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>-0.03702171479760257</v>
+        <v>0.03519327060819308</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.004613427582381717</v>
+        <v>-0.02620179575956627</v>
       </c>
       <c r="EB4" t="n">
         <v>-0</v>
       </c>
       <c r="EC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
         <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.03230339675852074</v>
+        <v>-0.0288250938849851</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.02538941255373009</v>
+        <v>0.02657627520830496</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.01070925932894569</v>
+        <v>0.007217712608020624</v>
       </c>
       <c r="EK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.06634190169470758</v>
+        <v>-0.0302076389750224</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0.02425858359178457</v>
+        <v>-0.03317445824009699</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.004815607128464339</v>
+        <v>-0.00759227568670947</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.0724069579026401</v>
+        <v>-0.05782793828799006</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.01642256693566067</v>
+        <v>0.03907713619851726</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.01939109198062648</v>
+        <v>0.0003652859307022828</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.01712536775391619</v>
+        <v>-0.0183136365930051</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.02286720909739108</v>
+        <v>0.007518419956637944</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.01248380677439658</v>
+        <v>-0.001099803550039057</v>
       </c>
       <c r="FL4" t="n">
         <v>0</v>
       </c>
       <c r="FM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN4" t="n">
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.001965742858015219</v>
+        <v>0.002187470790602262</v>
       </c>
       <c r="FR4" t="n">
         <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>-0.01345454833208636</v>
+        <v>0.0498087111696518</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0001235342325441958</v>
+        <v>-0.0005226500036807407</v>
       </c>
       <c r="FU4" t="n">
         <v>0</v>
@@ -2677,28 +2677,28 @@
         <v>0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.01321071529631316</v>
+        <v>-0.0382967940281741</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>-0.02936424052690993</v>
+        <v>0.01271678053546826</v>
       </c>
       <c r="GC4" t="n">
         <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
         <v>-0</v>
@@ -2709,25 +2709,25 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.02268439478384034</v>
+        <v>0.1204962894122573</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.02747027646205344</v>
+        <v>0.04372102862029235</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.01188726581657177</v>
+        <v>-0.03651679370974738</v>
       </c>
       <c r="G5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2736,52 +2736,52 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003287494626539848</v>
+        <v>0.06866853677767326</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.008522421853064063</v>
+        <v>0.002474931025455624</v>
       </c>
       <c r="O5" t="n">
-        <v>0.006071276109088074</v>
+        <v>0.01941424806559894</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.005353888146748918</v>
+        <v>0.07464311865299823</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.02576338388701627</v>
+        <v>-0.06129222663086852</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01809012720518018</v>
+        <v>0.02380967796376977</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>-0</v>
@@ -2790,34 +2790,34 @@
         <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.002530348194942028</v>
+        <v>-0.006991363382413029</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.001501647096686009</v>
+        <v>-0.0130265199864721</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.001039678282995042</v>
+        <v>-0.002046322213688674</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01217833855393301</v>
+        <v>0.07365219490376265</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
@@ -2826,37 +2826,37 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.02120299402765552</v>
+        <v>0.04621702993397638</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.005849068335385088</v>
+        <v>-0.06568827518290088</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.04728248793561657</v>
+        <v>0.2575989264394207</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.06293606173153489</v>
+        <v>-0.06208708722164234</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.01923282540108687</v>
+        <v>-0.1018981168364619</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2865,28 +2865,28 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.003194273847711181</v>
+        <v>-0.0002451638230652542</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.002064309332580687</v>
+        <v>7.421282029565765e-05</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.001103043414109753</v>
+        <v>0.004837971057444258</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
         <v>-0</v>
@@ -2895,28 +2895,28 @@
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.03558707422729945</v>
+        <v>0.003081546092768111</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.01600879544219332</v>
+        <v>0.06852663565613308</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.01072376823458696</v>
+        <v>0.07653643826289878</v>
       </c>
       <c r="BR5" t="n">
         <v>-0</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT5" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.02127014139209268</v>
+        <v>0.2373284017045959</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,13 +2934,13 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.02381930171837833</v>
+        <v>0.01206150151269449</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.006067392019661906</v>
+        <v>-0.0473280377267262</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
         <v>0</v>
@@ -2952,7 +2952,7 @@
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.003471499115641525</v>
+        <v>-0.07833857347927332</v>
       </c>
       <c r="CF5" t="n">
         <v>-0</v>
@@ -2961,13 +2961,13 @@
         <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.01457479914544776</v>
+        <v>-0.04355038302228902</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.01471896964045712</v>
+        <v>0.05289467249391129</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK5" t="n">
         <v>0</v>
@@ -2976,37 +2976,37 @@
         <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.004087901282170713</v>
+        <v>-0.06441154149646841</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.00387881397542316</v>
+        <v>0.01332551910201446</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.005457330459562378</v>
+        <v>0.02460445577919756</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.003388255646039232</v>
+        <v>-0.06824148502604621</v>
       </c>
       <c r="CX5" t="n">
         <v>0</v>
@@ -3015,16 +3015,16 @@
         <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.01437546518236711</v>
+        <v>-0.05150452622518162</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.02191984448579075</v>
+        <v>0.05082377073470604</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD5" t="n">
         <v>0</v>
@@ -3033,19 +3033,19 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.0162778035752915</v>
+        <v>-0.01555563275203401</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.0218657034508133</v>
+        <v>-0.05140236442280911</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.003843992597634846</v>
+        <v>0.00397261130215244</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
@@ -3054,31 +3054,31 @@
         <v>-0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.006620892075741899</v>
+        <v>-0.05218010492088184</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.01770089194230294</v>
+        <v>-0.003768880745632155</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.01140695356321716</v>
+        <v>-0.003184535558826215</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
@@ -3087,19 +3087,19 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.02091407789034774</v>
+        <v>0.06400155833574853</v>
       </c>
       <c r="DY5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ5" t="n">
         <v>0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.02139175419288739</v>
+        <v>-0.06439876731727406</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.002192802872404523</v>
+        <v>0.06879048248443873</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
@@ -3114,34 +3114,34 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.001000834032403351</v>
+        <v>-0.000625683881139631</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.0001184718245920088</v>
+        <v>-0.08397975330160659</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.01723928961783006</v>
+        <v>-0.0009557271776534181</v>
       </c>
       <c r="EL5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.01288615089301984</v>
+        <v>-0.03070501915610401</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
@@ -3150,25 +3150,25 @@
         <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.02685648780244497</v>
+        <v>-0.1222582654596189</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.01155618032641743</v>
+        <v>0.06450202250786367</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
         <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.007092372030408864</v>
+        <v>-0.07648814945207111</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
@@ -3177,16 +3177,16 @@
         <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.01359019080111006</v>
+        <v>-0.06159792234824982</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.01817641942157775</v>
+        <v>0.03644461513703364</v>
       </c>
       <c r="FD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF5" t="n">
         <v>-0</v>
@@ -3195,46 +3195,46 @@
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.02378273299684842</v>
+        <v>-0.04006205895279902</v>
       </c>
       <c r="FI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ5" t="n">
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.03118629218463316</v>
+        <v>-0.01796765693413403</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.01345096143099394</v>
+        <v>0.02107087111854474</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.002019230471788759</v>
+        <v>0.02015973048869393</v>
       </c>
       <c r="FR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0003728966889682494</v>
+        <v>0.004773663552927463</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.02138317414574403</v>
+        <v>-0.06082422783376076</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
@@ -3246,10 +3246,10 @@
         <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.01280916816419569</v>
+        <v>-0.04227178119348107</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.0006918059517758503</v>
+        <v>0.02210603320710807</v>
       </c>
       <c r="GE5" t="n">
         <v>0</v>
@@ -3847,16 +3847,16 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9035793118895268</v>
+        <v>0.0926890662451596</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2047410576605773</v>
+        <v>-0.03076123903081899</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.03013546397048326</v>
+        <v>-0.01411152122102828</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,22 +3868,22 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4311206322098992</v>
+        <v>0.07480578207134746</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.04957543427231225</v>
+        <v>0.01123661151656638</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.07744780162500549</v>
+        <v>-0.01561910294253846</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3898,79 +3898,79 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2560506663377659</v>
+        <v>0.02994407278719569</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2809579461926515</v>
+        <v>-0.02754529766158811</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.1336849081792081</v>
+        <v>-0.02505496046819287</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.03760742693180052</v>
+        <v>-0.002227368136349436</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.02094633769221316</v>
+        <v>-0.003722141407356075</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.01075126272495066</v>
+        <v>-0.008487731806093461</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.2216374686334281</v>
+        <v>0.07232013663858615</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.1914137477203823</v>
+        <v>-0.02360845745979273</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.1218597554810633</v>
+        <v>0.02238535138807621</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
@@ -3982,16 +3982,16 @@
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.543484617358643</v>
+        <v>0.1719234379081167</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.147632210059525</v>
+        <v>-0.06008875361530004</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.4476024968218165</v>
+        <v>-0.065304558349045</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
@@ -4000,25 +4000,25 @@
         <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.06374880283070006</v>
+        <v>-0.008691878651543833</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.0353259428399913</v>
+        <v>-0.004950849204391925</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1041513198505776</v>
+        <v>-0.007063548680499985</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,31 +4027,31 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.2460144739782524</v>
+        <v>0.002163269863227328</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.3735607467130891</v>
+        <v>0.01600281065215024</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1110003188420241</v>
+        <v>0.04304353968754866</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4063,25 +4063,25 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.7837100444794427</v>
+        <v>0.1194094341631819</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.06559868132185916</v>
+        <v>-0.03093940129176221</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.006530813514490842</v>
+        <v>-0.008777828646371829</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
@@ -4090,46 +4090,46 @@
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.3279826472964104</v>
+        <v>-0.05273255975085293</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.07006199026126286</v>
+        <v>0.04223888059878741</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.1044396460429672</v>
+        <v>0.005504112767379742</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.001111615230024772</v>
+        <v>-0.02796949619066849</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.3263564152713813</v>
+        <v>0.05521072426925243</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.317615899110868</v>
+        <v>0.03671907319482148</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,52 +4138,52 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.2576734416699612</v>
+        <v>-0.05544065699301207</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.1931762909607523</v>
+        <v>0.04796322814102252</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.09838445605056975</v>
+        <v>0.01029270943403454</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.128076658373489</v>
+        <v>-0.01917213413698758</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.0365132132919329</v>
+        <v>-0.004760548039488651</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.02319486972660373</v>
+        <v>-0.006347124716741872</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK7" t="n">
         <v>0</v>
@@ -4198,19 +4198,19 @@
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.1602784655793328</v>
+        <v>-0.03482325816399452</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.1424009909686813</v>
+        <v>0.01269693031307704</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.1034556297995141</v>
+        <v>-0.02949595788002673</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
@@ -4225,22 +4225,22 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.004406146652834937</v>
+        <v>0.009023032062985768</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.1161441627749348</v>
+        <v>0.02585363005154738</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.2614590051648251</v>
+        <v>-0.009561809494138998</v>
       </c>
       <c r="EB7" t="n">
         <v>-0</v>
       </c>
       <c r="EC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED7" t="n">
         <v>0</v>
@@ -4249,52 +4249,52 @@
         <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1478696318677128</v>
+        <v>-0.03237982967448126</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.05931345595026899</v>
+        <v>0.03770431721818383</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.01713254493170627</v>
+        <v>0.00456954991734532</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.2638625378792682</v>
+        <v>-0.03113347500495947</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.2128412368343835</v>
+        <v>-0.02940725656719525</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.2150985888906532</v>
+        <v>-0.003153041954606379</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4306,43 +4306,43 @@
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.2691579000868343</v>
+        <v>-0.06057271537838322</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.12888654772227</v>
+        <v>0.04429424702669929</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.1220116524373601</v>
+        <v>0.003142085017760691</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.07571873918376425</v>
+        <v>-0.03545899895035158</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.1733517253826905</v>
+        <v>0.01444611704770025</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.07851313086769417</v>
+        <v>0.01930026165060133</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
@@ -4354,25 +4354,25 @@
         <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.07978725288363546</v>
+        <v>0.001709916428427405</v>
       </c>
       <c r="FR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>-0.2388637031090371</v>
+        <v>0.08496125159528514</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.2230601435678887</v>
+        <v>-0.01401828983413653</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
@@ -4381,34 +4381,34 @@
         <v>0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.1378404871462952</v>
+        <v>-0.03961811097555669</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.07799297895489993</v>
+        <v>0.00763063735752827</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4985,25 +4985,25 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.07564335821136696</v>
+        <v>0.108562443955464</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.006407900951717314</v>
+        <v>0.009498788432987173</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.02193417528879328</v>
+        <v>-0.03280805262204943</v>
       </c>
       <c r="G9" t="n">
         <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -5012,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02418979740657618</v>
+        <v>0.1367540840675727</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -5021,13 +5021,13 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.01766285917918023</v>
+        <v>-0.009374390563946487</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01276576830226924</v>
+        <v>0.009749047079063248</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>-0</v>
@@ -5036,49 +5036,49 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.001499044431806736</v>
+        <v>0.03658366716347307</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.01081333051941581</v>
+        <v>-0.0475665358007003</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01708747087080596</v>
+        <v>0.02503823481777379</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB9" t="n">
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.003383877750254</v>
+        <v>-0.003749111583034133</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.002490282837734659</v>
+        <v>-0.01043453473907667</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0004412523901840195</v>
+        <v>-0.000701948459574097</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
@@ -5087,13 +5087,13 @@
         <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0196914264670323</v>
+        <v>0.07461159697420967</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
@@ -5102,16 +5102,16 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.01724213785625251</v>
+        <v>0.004271231969763244</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.02512593275413193</v>
+        <v>-0.06710249962221698</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
@@ -5120,7 +5120,7 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.1198146277662278</v>
+        <v>0.2610975333495234</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -5129,52 +5129,52 @@
         <v>-0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.009596070704736118</v>
+        <v>-0.05948153348316591</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.0262815490100096</v>
+        <v>-0.07828403032224845</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.009712528649795066</v>
+        <v>-0.02321934992223472</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF9" t="n">
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.01298164735661382</v>
+        <v>-0.02543980173321047</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.001866192891557714</v>
+        <v>-0.003601353876775235</v>
       </c>
       <c r="BI9" t="n">
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.04051166551577459</v>
+        <v>0.008818033361773753</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
@@ -5183,43 +5183,43 @@
         <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.02534203739626778</v>
+        <v>0.0775689734539786</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.01508454525746601</v>
+        <v>0.05613158733426412</v>
       </c>
       <c r="BR9" t="n">
         <v>-0</v>
       </c>
       <c r="BS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.04434461478379526</v>
+        <v>0.1599971411151095</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.02630163098120585</v>
+        <v>-0.00295402503598435</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.02566012114410025</v>
+        <v>-0.02675570280512772</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
         <v>-0</v>
@@ -5228,79 +5228,79 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.01021633627072413</v>
+        <v>-0.04950747952212512</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.005493980705177336</v>
+        <v>0.001601745641644834</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.01861167248580702</v>
+        <v>0.03159493917898789</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.02149041624369045</v>
+        <v>-0.02899747201814791</v>
       </c>
       <c r="CO9" t="n">
         <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.004635497361002115</v>
+        <v>0.1014823323020002</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.03564906989834722</v>
+        <v>0.01625220050386796</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.002990897660925656</v>
+        <v>-0.04380372638224556</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.004340062308252478</v>
+        <v>0.00391126435959316</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.02606801133373826</v>
+        <v>0.03666461098331242</v>
       </c>
       <c r="DB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
@@ -5309,25 +5309,25 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.02160015794931227</v>
+        <v>0.00215220920930223</v>
       </c>
       <c r="DG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.02127922247846624</v>
+        <v>-0.0387227326753188</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.01894500925300325</v>
+        <v>0.06676634699647636</v>
       </c>
       <c r="DK9" t="n">
         <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
         <v>0</v>
@@ -5336,22 +5336,22 @@
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.001349013525961746</v>
+        <v>-0.03138441674098745</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
         <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.02113737799164414</v>
+        <v>-0.02404013461206335</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0.008559349005321565</v>
+        <v>0.0088405529306026</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
@@ -5363,25 +5363,25 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.03263680501306584</v>
+        <v>0.01301218421077817</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
         <v>0</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.05219673515619105</v>
+        <v>-0.08486517502321775</v>
       </c>
       <c r="EB9" t="n">
-        <v>-0.007642113263634216</v>
+        <v>0.01296225254465389</v>
       </c>
       <c r="EC9" t="n">
         <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
@@ -5390,100 +5390,100 @@
         <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.000183580520820375</v>
+        <v>0.008795829331390713</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.01305152982294512</v>
+        <v>-0.01952244635625345</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.00471269938363311</v>
+        <v>-0.01411673025046808</v>
       </c>
       <c r="EL9" t="n">
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.009156385893781262</v>
+        <v>-0.005467907495897348</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
         <v>0</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.02073135007653226</v>
+        <v>-0.09350713241218667</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0.05862331354878919</v>
+        <v>-0.1251509934316183</v>
       </c>
       <c r="EU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.003023023737394691</v>
+        <v>-0.05180829744105096</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.00488039821036206</v>
+        <v>-0.008811069094728684</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.02396460789911156</v>
+        <v>0.02126115967771795</v>
       </c>
       <c r="FD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.02218555438868567</v>
+        <v>-0.06009428772079779</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.0568279306925802</v>
+        <v>0.03704617339672418</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.005865709107281755</v>
+        <v>-0.0004317719610559441</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
@@ -5495,40 +5495,40 @@
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.004005650647232019</v>
+        <v>0.01494502210143982</v>
       </c>
       <c r="FR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS9" t="n">
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.02153467644438994</v>
+        <v>0.0104107732278716</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.05424689719892171</v>
+        <v>-0.08954999100902022</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.01985818623131706</v>
+        <v>-0.01267798480374294</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
         <v>-0</v>
@@ -5537,13 +5537,13 @@
         <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.005700945110349348</v>
+        <v>-0.02611354148988557</v>
       </c>
       <c r="GE9" t="n">
         <v>0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>0</v>
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.225533011979985</v>
+        <v>0.1383192497131776</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.06524666887302034</v>
+        <v>-0.04047714347917717</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.03297643226957468</v>
+        <v>-0.03275033946303852</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5575,22 +5575,22 @@
         <v>-0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.138982025617996</v>
+        <v>0.1220727922709067</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.01620771205212087</v>
+        <v>-0.01405970343180949</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0531607145799232</v>
+        <v>-0.04220618841963151</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -5602,85 +5602,85 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.06167130523479826</v>
+        <v>0.04565587352899402</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001292814327868412</v>
+        <v>-0.02534190296282061</v>
       </c>
       <c r="W10" t="n">
-        <v>0.03388604713161043</v>
+        <v>-0.0254583607983362</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.01145696742423894</v>
+        <v>-0.003228812940826687</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.007490165038909227</v>
+        <v>-0.005623883679767892</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.00026749222735671</v>
+        <v>-0.01246074149681489</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.02990530659681278</v>
+        <v>0.08055044920669127</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.06343253934764417</v>
+        <v>-0.01896567874559365</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.06968359795552445</v>
+        <v>0.02691929746108436</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -5689,16 +5689,16 @@
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.3799346429250625</v>
+        <v>0.1958684935731846</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.05104257085585302</v>
+        <v>-0.05891290496730259</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1844732457696621</v>
+        <v>-0.08511052087829565</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
@@ -5707,7 +5707,7 @@
         <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.006466091036233671</v>
+        <v>-0.0141808060483064</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.01639426221857669</v>
+        <v>-0.006058592943366517</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.05967563664840558</v>
+        <v>-0.01666309799093312</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
@@ -5743,22 +5743,22 @@
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.07667132726889651</v>
+        <v>0.00526370430109144</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.07099781111787186</v>
+        <v>0.01985798141616475</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1146987861668691</v>
+        <v>0.04380704861035413</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5770,130 +5770,130 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.1881463935573927</v>
+        <v>0.146422689610142</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0.01563640331358868</v>
+        <v>-0.05092065942222249</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.03100281082557191</v>
+        <v>-0.01732482118723023</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.06282185527356823</v>
+        <v>-0.05883343760126097</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.01137661944400312</v>
+        <v>0.04769815286569055</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.003148636784425464</v>
+        <v>0.007492870407360956</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.02853682380170865</v>
+        <v>-0.03826062732138996</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.07701194750110694</v>
+        <v>0.05447570223916458</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.1087275918098868</v>
+        <v>0.03298397753285158</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT10" t="n">
         <v>-0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.0398422882724583</v>
+        <v>-0.06025110120559061</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.03522287108180723</v>
+        <v>0.05439165247579222</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.005206918283826104</v>
+        <v>0.01362387001637884</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.0349217898945194</v>
+        <v>-0.05281988370393592</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.003071382060045882</v>
+        <v>0.0445731402379377</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.004698398764329929</v>
+        <v>-0.02362655946925039</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
         <v>0</v>
@@ -5905,208 +5905,208 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.05586174371940247</v>
+        <v>-0.0320069561300494</v>
       </c>
       <c r="DP10" t="n">
         <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.05208891419713636</v>
+        <v>0.01623177660861981</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.006409928284622499</v>
+        <v>-0.02805517703339241</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
         <v>0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.05074506032878022</v>
+        <v>0.02574779134057225</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.05172567480913145</v>
+        <v>0.02971952486581203</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.03865304014819306</v>
+        <v>-0.02340232296496138</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.02312737815105992</v>
+        <v>-0.02364517866491121</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.09059808485920383</v>
+        <v>0.0423133647798004</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.041946355481417</v>
+        <v>0.002755351552377102</v>
       </c>
       <c r="EK10" t="n">
         <v>-0</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN10" t="n">
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.07512527195402442</v>
+        <v>-0.03687729141050976</v>
       </c>
       <c r="EQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER10" t="n">
-        <v>-0.06486023817380196</v>
+        <v>-0.03574296669022008</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.01186726174378753</v>
+        <v>-0.01482420136853208</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.05589099140949527</v>
+        <v>-0.06767889493336211</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.0261542901580828</v>
+        <v>0.05199704801703266</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.00735058092204252</v>
+        <v>0.004098855249649697</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>-0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.06169620066810555</v>
+        <v>-0.03395653776716195</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.06628754441626686</v>
+        <v>0.02199697907443113</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.0280064668558163</v>
+        <v>0.01378424537964251</v>
       </c>
       <c r="FL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.02159428567919516</v>
+        <v>0.001043154416793875</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.01335093750879598</v>
+        <v>0.06121239582608083</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.02130778451119162</v>
+        <v>-0.02272327452677005</v>
       </c>
       <c r="FU10" t="n">
         <v>0</v>
       </c>
       <c r="FV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.02436903292788184</v>
+        <v>-0.03792406521552467</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.02751982060809865</v>
+        <v>0.003402375167939409</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
@@ -6115,7 +6115,7 @@
         <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6692,43 +6692,43 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2319314309948152</v>
+        <v>0.0573162775182251</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0100959280169036</v>
+        <v>-0.005674550210874319</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.03377362663904359</v>
+        <v>-0.01850332010907028</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1241429097272778</v>
+        <v>0.06384305483805441</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.008924056870393986</v>
+        <v>0.005544215767195043</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.03347733249180852</v>
+        <v>-0.02525238084277283</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6740,25 +6740,25 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.06449272340137711</v>
+        <v>0.02372218030276372</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.01946502971265361</v>
+        <v>-0.01379703840636161</v>
       </c>
       <c r="W12" t="n">
-        <v>0.04854096347096663</v>
+        <v>-0.004448866603222068</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -6770,46 +6770,46 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.008796142279276897</v>
+        <v>-0.0004069743742048102</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.00111039505353517</v>
+        <v>-0.004143672196251794</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.001256270620613282</v>
+        <v>-0.003127787684094991</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.0010744729176884</v>
+        <v>0.03787363906383692</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.0223315946852491</v>
+        <v>-0.003013557074792699</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.03862587309262748</v>
+        <v>0.03185642407245431</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6818,52 +6818,52 @@
         <v>-0</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.3086355402475284</v>
+        <v>0.09655077784757433</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.0283314758242729</v>
+        <v>-0.008860122278859009</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.08825149684463385</v>
+        <v>-0.05080297376130665</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.02187665864393959</v>
+        <v>-0.01825545628178669</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.02430896308296026</v>
+        <v>-0.001540342480061753</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.03142391274570306</v>
+        <v>-0.008964641927935311</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,19 +6881,19 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1012769859100542</v>
+        <v>0.02625172209399775</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.01535697156953544</v>
+        <v>0.006797896142057315</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1180597831587158</v>
+        <v>0.03429731615612348</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
         <v>0</v>
@@ -6908,43 +6908,43 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1565867267490491</v>
+        <v>0.0703010162060287</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.01758366981166867</v>
+        <v>-0.02247447296256884</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.03314062831018278</v>
+        <v>-0.01549816780775764</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.06161854368092072</v>
+        <v>-0.02249719012240543</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0.005423586254679604</v>
+        <v>0.01752752822717481</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.004765472206102902</v>
+        <v>0.01044780063599123</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
@@ -6962,43 +6962,43 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.0455756601074926</v>
+        <v>-0.03425333922267983</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.04077594151277887</v>
+        <v>0.02212425741805508</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.0750462677456873</v>
+        <v>0.03285392381955901</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
         <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.04331958218763234</v>
+        <v>-0.02335205320528036</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.006810634070901651</v>
+        <v>0.02178700258716177</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.003358865459569609</v>
+        <v>0.01042288594486182</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
@@ -7007,106 +7007,106 @@
         <v>0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.01436609010524709</v>
+        <v>0.001102473468490682</v>
       </c>
       <c r="DG12" t="n">
         <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.03163077236988403</v>
+        <v>0.005877357715080629</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.008545199827349343</v>
+        <v>-0.002350346203528675</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
         <v>-0</v>
       </c>
       <c r="DL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM12" t="n">
         <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.07040451428474941</v>
+        <v>-0.02490936581112762</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.01501051966026627</v>
+        <v>-0.01697713441052554</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.005065437880365199</v>
+        <v>-0.02164922773404901</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.01245641000131974</v>
+        <v>0.03427162550501182</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.02282603734545656</v>
+        <v>0.01984154965597438</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.03788656597738447</v>
+        <v>-0.03474793908836647</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
         <v>0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.03578775150576195</v>
+        <v>0.0008489708232565111</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.00833347149077188</v>
+        <v>0.009081349480534101</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.02638518437627661</v>
+        <v>0.01986858115364892</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
@@ -7115,7 +7115,7 @@
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
@@ -7124,25 +7124,25 @@
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.04437526016804733</v>
+        <v>-0.004845518750225359</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>-0.00255299087769483</v>
+        <v>0.01071925538800148</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.02113951912504448</v>
+        <v>0.00699338527232572</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW12" t="n">
         <v>-0</v>
@@ -7151,16 +7151,16 @@
         <v>0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.04608206538336353</v>
+        <v>-0.02716521819103432</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.0006202041226931699</v>
+        <v>0.02473073059353463</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.01823834804567494</v>
+        <v>0.007066221135031843</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
@@ -7169,61 +7169,61 @@
         <v>-0</v>
       </c>
       <c r="FE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF12" t="n">
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.02678045310315862</v>
+        <v>0.004446790371169682</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.0186468906669528</v>
+        <v>0.002934729054838652</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.01474953403983747</v>
+        <v>-0.01603365775224148</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.05384769988992936</v>
+        <v>0.01529088860505949</v>
       </c>
       <c r="FR12" t="n">
         <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.04179581499436907</v>
+        <v>0.03063491669797924</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.003263234232732028</v>
+        <v>-0.04060731636553413</v>
       </c>
       <c r="FU12" t="n">
         <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
         <v>0</v>
@@ -7232,28 +7232,28 @@
         <v>-0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>8.143383890262326e-05</v>
+        <v>0.001659829399025825</v>
       </c>
       <c r="GA12" t="n">
         <v>-0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.03896565604373283</v>
+        <v>-0.004464733388819545</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF12" t="n">
         <v>0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,22 +7261,22 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2999049168023377</v>
+        <v>0.07448933425452281</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.004338926335381067</v>
+        <v>-0.02607885892319155</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1625406168637643</v>
+        <v>-0.03801844780667329</v>
       </c>
       <c r="G13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>-0</v>
@@ -7288,25 +7288,25 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2062381199368893</v>
+        <v>0.1156567664814084</v>
       </c>
       <c r="L13" t="n">
         <v>-0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.01158300247194104</v>
+        <v>-0.05126848081646183</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1193056933867729</v>
+        <v>-0.02370155830507869</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,7 +7315,7 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.02034486464417989</v>
+        <v>0.02960544540076145</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -7324,25 +7324,25 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.0566635556702445</v>
+        <v>-0.001166778218406714</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.01594750389689767</v>
+        <v>-0.004468825209583923</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB13" t="n">
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.01058354587902371</v>
+        <v>-0.0004099152194581036</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -7351,10 +7351,10 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.00495453417050269</v>
+        <v>-0.009156938293333583</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.001226988135615982</v>
+        <v>-0.0005220652231399603</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7363,13 +7363,13 @@
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.04157731531539819</v>
+        <v>0.03665565439844577</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
@@ -7378,13 +7378,13 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.04219530298594017</v>
+        <v>0.01882637388202938</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.0886158144608723</v>
+        <v>-0.02017991720561206</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7393,37 +7393,37 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.2983907796270931</v>
+        <v>0.1280312295795228</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.01309534324111874</v>
+        <v>-0.04503376146097193</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.1364801009071201</v>
+        <v>-0.04876055987758231</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.06921758529246701</v>
+        <v>-0.01438078160754493</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,25 +7432,25 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.03408035281060902</v>
+        <v>-0.02337076978341307</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.03173194433505527</v>
+        <v>-0.01099941177881783</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1143004321224775</v>
+        <v>0.01968136182985886</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
@@ -7459,37 +7459,37 @@
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.05504035762627552</v>
+        <v>0.0468051152650822</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.0184399095743182</v>
+        <v>0.005717598638355663</v>
       </c>
       <c r="BR13" t="n">
         <v>-0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.1378698315745481</v>
+        <v>0.1094030478249001</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.03150494885924501</v>
+        <v>-0.006115916411166026</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.0247519131430428</v>
+        <v>-0.02037393136736652</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7504,46 +7504,46 @@
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.06963667168657564</v>
+        <v>-0.03931999372353598</v>
       </c>
       <c r="CF13" t="n">
         <v>0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.01839808569998799</v>
+        <v>0.0141390926747268</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.05199944374476929</v>
+        <v>0.03295142094131694</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.02232930187659569</v>
+        <v>-0.08528769520085457</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.02039804023083297</v>
+        <v>0.04240461610842111</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.06874259102419711</v>
+        <v>0.04559864443989804</v>
       </c>
       <c r="CS13" t="n">
         <v>-0</v>
@@ -7552,52 +7552,52 @@
         <v>-0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
         <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.04886679233457203</v>
+        <v>-0.0321603782513426</v>
       </c>
       <c r="CX13" t="n">
         <v>-0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.01781172990997879</v>
+        <v>0.01164125175703547</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.05187609282384185</v>
+        <v>0.03320218734379622</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
       </c>
       <c r="DC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD13" t="n">
         <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.007922151093282695</v>
+        <v>0.0004768969262791982</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.005317611792539655</v>
+        <v>-0.01177593290301441</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-0.001458112989499492</v>
+        <v>0.0109970550092289</v>
       </c>
       <c r="DK13" t="n">
         <v>0</v>
@@ -7606,25 +7606,25 @@
         <v>-0</v>
       </c>
       <c r="DM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN13" t="n">
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.03040784280164529</v>
+        <v>-0.03306972471634458</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
         <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.03419203812704002</v>
+        <v>0.03105267470618402</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.01598615620768625</v>
+        <v>-0.02141349035850165</v>
       </c>
       <c r="DT13" t="n">
         <v>0</v>
@@ -7639,22 +7639,22 @@
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.01975319210083409</v>
+        <v>0.02668045416839687</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.04400395796334482</v>
+        <v>-0.007519778312301256</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.008193666248519485</v>
+        <v>-0.07368972747995417</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
         <v>0</v>
@@ -7666,7 +7666,7 @@
         <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.03459412103240409</v>
+        <v>0.01578360762003438</v>
       </c>
       <c r="EH13" t="n">
         <v>0</v>
@@ -7675,79 +7675,79 @@
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.004746942285684793</v>
+        <v>-0.003358561426299297</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.04012400163619731</v>
+        <v>0.02186698458463069</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
       </c>
       <c r="EM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.0528035098482517</v>
+        <v>-0.01964810788601276</v>
       </c>
       <c r="EQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.04292728248716164</v>
+        <v>-0.02094733331818075</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.1013356786119569</v>
+        <v>0.02744093080420752</v>
       </c>
       <c r="EU13" t="n">
         <v>-0</v>
       </c>
       <c r="EV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
         <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.0486219414528235</v>
+        <v>-0.04105958369095662</v>
       </c>
       <c r="EZ13" t="n">
         <v>0</v>
       </c>
       <c r="FA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.01565337858076206</v>
+        <v>0.005752616871517659</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.0551550547662986</v>
+        <v>0.02906758317182959</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.02458211581775934</v>
+        <v>-0.02305245322314368</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,37 +7756,37 @@
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.04837898900104246</v>
+        <v>9.826206848937621e-05</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.02352744963525517</v>
+        <v>0.005347802115566806</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.02356662639804594</v>
+        <v>-0.004978135441314245</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.03710584364049012</v>
+        <v>-0.01940892612572696</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.003390495091217313</v>
+        <v>-0.0001420598052796303</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
@@ -7795,13 +7795,13 @@
         <v>-0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.03305337741540911</v>
+        <v>-0.001157296371322919</v>
       </c>
       <c r="GA13" t="n">
         <v>-0</v>
@@ -7813,13 +7813,13 @@
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.0425441139598616</v>
+        <v>0.003215326705760291</v>
       </c>
       <c r="GE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
         <v>0</v>
@@ -7830,70 +7830,70 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.07320315176972168</v>
+        <v>-0.02127013957993951</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1805069664768639</v>
+        <v>0.01633146672714855</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.05651082784157111</v>
+        <v>-0.04415939297633666</v>
       </c>
       <c r="F14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
         <v>-0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.07752459460238795</v>
+        <v>-0.0184836938203624</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2059083821109485</v>
+        <v>0.01024694388844534</v>
       </c>
       <c r="N14" t="n">
-        <v>0.03190872033815686</v>
+        <v>-0.04325406724954327</v>
       </c>
       <c r="O14" t="n">
         <v>-0</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R14" t="n">
         <v>-0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.03741073967491936</v>
+        <v>-0.004999743456996134</v>
       </c>
       <c r="V14" t="n">
-        <v>0.06110610270369986</v>
+        <v>0.02146402378323126</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0005190040934136445</v>
+        <v>0.004432483022922988</v>
       </c>
       <c r="X14" t="n">
         <v>-0</v>
@@ -7905,22 +7905,22 @@
         <v>-0</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.01330719598361956</v>
+        <v>-0.009004367705412616</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.01026129744745851</v>
+        <v>-0.008899127340658855</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.005294871048914178</v>
+        <v>-0.005325274330281211</v>
       </c>
       <c r="AG14" t="n">
         <v>-0</v>
@@ -7935,46 +7935,46 @@
         <v>-0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.001974661845834691</v>
+        <v>-0.0306327486242105</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.04326483674224554</v>
+        <v>0.02528605761696869</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.03716486823680068</v>
+        <v>-0.0002429563454847914</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0.08476368103805369</v>
+        <v>-0.03298207614365769</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.137920974387504</v>
+        <v>0.08560974498632433</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.1668513816665699</v>
+        <v>-0.0663500406979181</v>
       </c>
       <c r="AY14" t="n">
         <v>0</v>
@@ -7995,13 +7995,13 @@
         <v>-0</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.01535059704033053</v>
+        <v>-0.00360501124954469</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.01415120710031208</v>
+        <v>-0.06277095368738325</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.01066772897341116</v>
+        <v>-0.03001137893012848</v>
       </c>
       <c r="BH14" t="n">
         <v>-0</v>
@@ -8010,109 +8010,109 @@
         <v>0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>-0</v>
       </c>
       <c r="BL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.02702798814598809</v>
+        <v>0.02219225272085025</v>
       </c>
       <c r="BO14" t="n">
-        <v>-0.02297240353062143</v>
+        <v>0.03604978676513173</v>
       </c>
       <c r="BP14" t="n">
-        <v>-0.1158670216789076</v>
+        <v>0.0576692690815058</v>
       </c>
       <c r="BQ14" t="n">
         <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW14" t="n">
-        <v>-0.09535055230670218</v>
+        <v>-0.02760860240020581</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.1029256284365621</v>
+        <v>0.08505825211509865</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.1077701441162298</v>
+        <v>-0.01174575314935965</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE14" t="n">
         <v>0</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.04484757410625384</v>
+        <v>0.02432624599869514</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0.04517434325612559</v>
+        <v>0.004969817100410077</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.006827932314362701</v>
+        <v>0.009187152478824316</v>
       </c>
       <c r="CI14" t="n">
         <v>-0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL14" t="n">
         <v>0</v>
       </c>
       <c r="CM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.01100267620142521</v>
+        <v>0.007761986719222579</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.05169598248615494</v>
+        <v>0.01901922236941934</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.0812546082340118</v>
+        <v>0.04662779561221762</v>
       </c>
       <c r="CR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS14" t="n">
         <v>-0</v>
@@ -8121,7 +8121,7 @@
         <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV14" t="n">
         <v>-0</v>
@@ -8130,19 +8130,19 @@
         <v>-0</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.03060940878414249</v>
+        <v>0.01792159626564429</v>
       </c>
       <c r="CY14" t="n">
-        <v>-0.03856775046384766</v>
+        <v>0.003944029660510682</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.01148044299878539</v>
+        <v>0.01681825724117706</v>
       </c>
       <c r="DA14" t="n">
         <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC14" t="n">
         <v>-0</v>
@@ -8154,19 +8154,19 @@
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.004396798827183517</v>
+        <v>0.01163266494791936</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0.04270903995061074</v>
+        <v>-0.0175318718018731</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.001950658893485072</v>
+        <v>-8.198801574280764e-05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK14" t="n">
         <v>0</v>
@@ -8175,22 +8175,22 @@
         <v>-0</v>
       </c>
       <c r="DM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO14" t="n">
         <v>0</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.01867127047016726</v>
+        <v>0.002571687708827206</v>
       </c>
       <c r="DQ14" t="n">
-        <v>-0.02316302816365882</v>
+        <v>-0.004349982620657404</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.04346955794530389</v>
+        <v>0.03602932092999065</v>
       </c>
       <c r="DS14" t="n">
         <v>-0</v>
@@ -8199,25 +8199,25 @@
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY14" t="n">
-        <v>-0.003298204947581754</v>
+        <v>-0.02853172621130505</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.03020194557932186</v>
+        <v>-0.01287371112845856</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.03242722204179267</v>
+        <v>-0.03345999263083237</v>
       </c>
       <c r="EB14" t="n">
         <v>-0</v>
@@ -8226,7 +8226,7 @@
         <v>0</v>
       </c>
       <c r="ED14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE14" t="n">
         <v>0</v>
@@ -8235,22 +8235,22 @@
         <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.05302305440249342</v>
+        <v>0.0003141996717623252</v>
       </c>
       <c r="EI14" t="n">
-        <v>-0.05620237698295018</v>
+        <v>0.01330368643034649</v>
       </c>
       <c r="EJ14" t="n">
-        <v>-0.01051330868886719</v>
+        <v>-0.001619699217362311</v>
       </c>
       <c r="EK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM14" t="n">
         <v>0</v>
@@ -8259,124 +8259,124 @@
         <v>0</v>
       </c>
       <c r="EO14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.02563203763469301</v>
+        <v>-0.005738181128006337</v>
       </c>
       <c r="ER14" t="n">
-        <v>-0.01464243848179804</v>
+        <v>-0.01133801947378917</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.01983645814677744</v>
+        <v>0.008161054186915097</v>
       </c>
       <c r="ET14" t="n">
         <v>-0</v>
       </c>
       <c r="EU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.03448477922187294</v>
+        <v>0.0182322885487567</v>
       </c>
       <c r="FA14" t="n">
-        <v>-0.04025311367805657</v>
+        <v>-0.004701396421623079</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.01622576804014874</v>
+        <v>0.01100864092692808</v>
       </c>
       <c r="FC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE14" t="n">
         <v>-0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.01968590165176663</v>
+        <v>0.02359552181810509</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.03009585675977385</v>
+        <v>-0.006436576944545347</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.03025935797058418</v>
+        <v>-0.0418004592839918</v>
       </c>
       <c r="FL14" t="n">
         <v>0</v>
       </c>
       <c r="FM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
         <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.009814154324666754</v>
+        <v>-0.001640991874446888</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.003307008304774442</v>
+        <v>0.003937747460786307</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.02305995836792224</v>
+        <v>0.03445099079178188</v>
       </c>
       <c r="FU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV14" t="n">
         <v>0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.02863456512655745</v>
+        <v>0.0157084586030575</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.03896338820359124</v>
+        <v>-0.0253079647576182</v>
       </c>
       <c r="GC14" t="n">
         <v>0</v>
@@ -8385,13 +8385,13 @@
         <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="15">
@@ -8965,25 +8965,25 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.2425959059475608</v>
+        <v>0.194042883333146</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.2044012584048431</v>
+        <v>-0.04590859121935954</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0576792711272106</v>
+        <v>-0.07836824418724603</v>
       </c>
       <c r="G16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>-0</v>
@@ -8995,7 +8995,7 @@
         <v>-0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1646667280087377</v>
+        <v>0.2880133930988162</v>
       </c>
       <c r="L16" t="n">
         <v>-0</v>
@@ -9004,13 +9004,13 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1913781699236009</v>
+        <v>-0.1021067073510686</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.06941890052850815</v>
+        <v>-0.0837859526230636</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -9022,7 +9022,7 @@
         <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.05630864461352614</v>
+        <v>0.08159116912860709</v>
       </c>
       <c r="U16" t="n">
         <v>-0</v>
@@ -9031,37 +9031,37 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.01892120295511485</v>
+        <v>-0.05266273833678933</v>
       </c>
       <c r="X16" t="n">
-        <v>0.04796521046911042</v>
+        <v>0.01041551244047977</v>
       </c>
       <c r="Y16" t="n">
         <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB16" t="n">
         <v>-0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.02440837658118449</v>
+        <v>-0.01846015068105302</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.004007845248035823</v>
+        <v>-0.05053942535041074</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.005340993750664104</v>
+        <v>0.01498974585507056</v>
       </c>
       <c r="AH16" t="n">
         <v>-0</v>
@@ -9070,13 +9070,13 @@
         <v>-0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.06749983798617464</v>
+        <v>0.02062353115615116</v>
       </c>
       <c r="AM16" t="n">
         <v>-0</v>
@@ -9085,145 +9085,145 @@
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>-0.02384608812256462</v>
+        <v>-0.07816295433846263</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.03092866274598175</v>
+        <v>-0.03461508913461926</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
         <v>-0</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT16" t="n">
         <v>-0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.236035049306716</v>
+        <v>0.3843583789775313</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.1158333674903498</v>
+        <v>-0.1671793990195938</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.0422676882986994</v>
+        <v>-0.1252372346124552</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>-0</v>
       </c>
       <c r="BC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.05285293868446759</v>
+        <v>-0.07276065626108297</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.1020362028649514</v>
+        <v>-0.02797902702231792</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.02045422452613465</v>
+        <v>0.01819877297725249</v>
       </c>
       <c r="BI16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.09356470008599962</v>
+        <v>0.1166615012101952</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.03469693571817163</v>
+        <v>0.1128748882364791</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.04573088887260311</v>
+        <v>0.06024910472197777</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
         <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.1381237225757605</v>
+        <v>0.2254606609990919</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX16" t="n">
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.05019722718261577</v>
+        <v>-0.05696892797631312</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.02392306160621485</v>
+        <v>-0.02695553337389237</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD16" t="n">
         <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.0420513120971573</v>
+        <v>-0.06731495285708639</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.03466343784050077</v>
+        <v>0.04354077889299127</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.02605332197169696</v>
+        <v>0.02981296603959213</v>
       </c>
       <c r="CJ16" t="n">
         <v>-0</v>
@@ -9232,52 +9232,52 @@
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.0279722640232389</v>
+        <v>-0.1539632208721513</v>
       </c>
       <c r="CO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP16" t="n">
         <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>-0.01009084835676654</v>
+        <v>0.12577948595803</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.008868919385551635</v>
+        <v>-0.00921155747150435</v>
       </c>
       <c r="CS16" t="n">
         <v>-0</v>
       </c>
       <c r="CT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.02251114411176981</v>
+        <v>-0.0613355533704437</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.02998053167577898</v>
+        <v>0.02098028513922486</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.03481907893876882</v>
+        <v>0.03912692846797455</v>
       </c>
       <c r="DB16" t="n">
         <v>0</v>
@@ -9289,49 +9289,49 @@
         <v>0</v>
       </c>
       <c r="DE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.04056751595339051</v>
+        <v>-0.06146081020505646</v>
       </c>
       <c r="DG16" t="n">
         <v>-0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.02902935837641452</v>
+        <v>-0.02930421027363694</v>
       </c>
       <c r="DJ16" t="n">
-        <v>-0.004596469073193308</v>
+        <v>-0.02323394337036962</v>
       </c>
       <c r="DK16" t="n">
         <v>0</v>
       </c>
       <c r="DL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.03920374967035457</v>
+        <v>-0.01894824367096069</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.02138179213672422</v>
+        <v>-0.006381938889982141</v>
       </c>
       <c r="DS16" t="n">
-        <v>-0.06351282490032399</v>
+        <v>-0.04280266956956144</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
@@ -9346,7 +9346,7 @@
         <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.009253498828676049</v>
+        <v>0.05767317248348006</v>
       </c>
       <c r="DY16" t="n">
         <v>0</v>
@@ -9355,37 +9355,37 @@
         <v>0</v>
       </c>
       <c r="EA16" t="n">
-        <v>-0.06126472510917763</v>
+        <v>-0.06182087476115457</v>
       </c>
       <c r="EB16" t="n">
-        <v>-0.04836842406183646</v>
+        <v>-0.01356714575413881</v>
       </c>
       <c r="EC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE16" t="n">
         <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.01666320555387084</v>
+        <v>-0.004537662359985893</v>
       </c>
       <c r="EH16" t="n">
         <v>-0</v>
       </c>
       <c r="EI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.02782827971552498</v>
+        <v>-0.01120922436409519</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.006794744682054581</v>
+        <v>0.02109375000599272</v>
       </c>
       <c r="EL16" t="n">
         <v>-0</v>
@@ -9394,52 +9394,52 @@
         <v>-0</v>
       </c>
       <c r="EN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>0.02440989632845985</v>
+        <v>0.008348671369656351</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
         <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.009288640033748992</v>
+        <v>-0.07211844518203059</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.05144178453946266</v>
+        <v>0.006260118924857999</v>
       </c>
       <c r="EU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV16" t="n">
         <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX16" t="n">
         <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.01904679600584331</v>
+        <v>-0.07788561358861494</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.02657218834782177</v>
+        <v>0.02610160817774057</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.03909592644804703</v>
+        <v>0.02036738717166649</v>
       </c>
       <c r="FD16" t="n">
         <v>-0</v>
@@ -9451,10 +9451,10 @@
         <v>-0</v>
       </c>
       <c r="FG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.04346366684427309</v>
+        <v>-0.06037764260167071</v>
       </c>
       <c r="FI16" t="n">
         <v>-0</v>
@@ -9463,16 +9463,16 @@
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>-0.04211409520999442</v>
+        <v>0.09219106019994897</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.02800492448756531</v>
+        <v>0.01603470144138039</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
@@ -9481,34 +9481,34 @@
         <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.00457378561851157</v>
+        <v>0.009055404036139235</v>
       </c>
       <c r="FR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS16" t="n">
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.005715581307481896</v>
+        <v>-0.02577905276520876</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.002915232104291577</v>
+        <v>-0.01967264140514236</v>
       </c>
       <c r="FV16" t="n">
         <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>-0.03753711130792133</v>
+        <v>-0.08843158049522434</v>
       </c>
       <c r="GA16" t="n">
         <v>0</v>
@@ -9517,19 +9517,19 @@
         <v>0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.03996723869842808</v>
+        <v>0.05102705633784577</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="17">
@@ -9537,16 +9537,16 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>0.5290779434981594</v>
+        <v>0.2899949438300385</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2171006433209222</v>
+        <v>-0.1440221743816</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1296753077154512</v>
+        <v>-0.01854783636578235</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -9564,16 +9564,16 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4346074427251523</v>
+        <v>0.3153322701879698</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2285234971552642</v>
+        <v>-0.171054953707122</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1787707474561575</v>
+        <v>-0.03470595469490437</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9588,52 +9588,52 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1363342061775303</v>
+        <v>0.0741832139533688</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.01276444556750737</v>
+        <v>-0.04181466247355142</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1014558818942988</v>
+        <v>-0.05989875239692612</v>
       </c>
       <c r="X17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>-0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.09942380230874853</v>
+        <v>-0.03784078816601482</v>
       </c>
       <c r="AD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>-2.61615169337044e-05</v>
+        <v>-0.03721179364056056</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0.001394804769572754</v>
+        <v>-0.04056266572697142</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>-0</v>
@@ -9645,22 +9645,22 @@
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.06836928206431077</v>
+        <v>0.1093058344135965</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN17" t="n">
-        <v>-0.03949474965513446</v>
+        <v>-0.07218015420832014</v>
       </c>
       <c r="AO17" t="n">
-        <v>-0.03212542438499771</v>
+        <v>0.03808822061796354</v>
       </c>
       <c r="AP17" t="n">
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
         <v>-0</v>
@@ -9669,28 +9669,28 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.4675044863450806</v>
+        <v>0.2814001807614349</v>
       </c>
       <c r="AV17" t="n">
         <v>-0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.005430277944769791</v>
+        <v>-0.0814640714510034</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.1273163744617277</v>
+        <v>-0.08711779444921106</v>
       </c>
       <c r="AY17" t="n">
         <v>-0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
         <v>-0</v>
@@ -9699,16 +9699,16 @@
         <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.0420351155623479</v>
+        <v>-0.01765351303710351</v>
       </c>
       <c r="BE17" t="n">
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>-0.08590150448645573</v>
+        <v>-0.03624121330011869</v>
       </c>
       <c r="BG17" t="n">
-        <v>-0.2039191237470565</v>
+        <v>-0.03940244726879383</v>
       </c>
       <c r="BH17" t="n">
         <v>0</v>
@@ -9717,7 +9717,7 @@
         <v>-0</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK17" t="n">
         <v>0</v>
@@ -9726,22 +9726,22 @@
         <v>-0</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.05468504335319181</v>
+        <v>-0.01663308053368364</v>
       </c>
       <c r="BN17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.0510034892803814</v>
+        <v>0.001902541934054675</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.06639355189181133</v>
+        <v>0.05935363949090264</v>
       </c>
       <c r="BQ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS17" t="n">
         <v>-0</v>
@@ -9753,22 +9753,22 @@
         <v>-0</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.2701821800661909</v>
+        <v>0.2185012438565757</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX17" t="n">
-        <v>-0.02965550798829323</v>
+        <v>-0.1034621799432813</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.07947086928307141</v>
+        <v>-0.03167234454628572</v>
       </c>
       <c r="BZ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB17" t="n">
         <v>0</v>
@@ -9780,46 +9780,46 @@
         <v>-0</v>
       </c>
       <c r="CE17" t="n">
-        <v>-0.113069112645768</v>
+        <v>-0.09559394135829961</v>
       </c>
       <c r="CF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.02608870191931243</v>
+        <v>0.08278238426657863</v>
       </c>
       <c r="CH17" t="n">
-        <v>-0.01566502370814961</v>
+        <v>0.003554310836044489</v>
       </c>
       <c r="CI17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK17" t="n">
         <v>0</v>
       </c>
       <c r="CL17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM17" t="n">
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>-0.04731086222033749</v>
+        <v>-0.1201326232822609</v>
       </c>
       <c r="CO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP17" t="n">
-        <v>-0.1036944846328819</v>
+        <v>0.1627875361696699</v>
       </c>
       <c r="CQ17" t="n">
-        <v>-0.1639779236006343</v>
+        <v>0.07615944587158113</v>
       </c>
       <c r="CR17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS17" t="n">
         <v>-0</v>
@@ -9828,28 +9828,28 @@
         <v>-0</v>
       </c>
       <c r="CU17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV17" t="n">
         <v>0</v>
       </c>
       <c r="CW17" t="n">
-        <v>-0.09820510343616375</v>
+        <v>-0.08707231988071078</v>
       </c>
       <c r="CX17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.03830590621789345</v>
+        <v>0.08840178014366126</v>
       </c>
       <c r="CZ17" t="n">
-        <v>-0.01688577581540018</v>
+        <v>0.005364337706190168</v>
       </c>
       <c r="DA17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC17" t="n">
         <v>-0</v>
@@ -9861,22 +9861,22 @@
         <v>0</v>
       </c>
       <c r="DF17" t="n">
-        <v>-0.05779809967280417</v>
+        <v>-0.08963779971636139</v>
       </c>
       <c r="DG17" t="n">
         <v>-0</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.01892618187383793</v>
+        <v>0.01405343515499719</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.02989879053501519</v>
+        <v>-0.04013432731381349</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL17" t="n">
         <v>0</v>
@@ -9885,25 +9885,25 @@
         <v>0</v>
       </c>
       <c r="DN17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO17" t="n">
-        <v>-0.04704771679673276</v>
+        <v>-0.04669859898377618</v>
       </c>
       <c r="DP17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ17" t="n">
-        <v>-0.03813754962809476</v>
+        <v>0.05417129624489551</v>
       </c>
       <c r="DR17" t="n">
-        <v>-0.08284070280116948</v>
+        <v>-0.007829551226788821</v>
       </c>
       <c r="DS17" t="n">
         <v>-0</v>
       </c>
       <c r="DT17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU17" t="n">
         <v>-0</v>
@@ -9912,25 +9912,25 @@
         <v>0</v>
       </c>
       <c r="DW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.05448105934707757</v>
+        <v>0.04293752855115764</v>
       </c>
       <c r="DY17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ17" t="n">
-        <v>-0.0256971304322998</v>
+        <v>-0.04200136923480653</v>
       </c>
       <c r="EA17" t="n">
-        <v>-0.0328002678757917</v>
+        <v>0.03307119659404372</v>
       </c>
       <c r="EB17" t="n">
         <v>0</v>
       </c>
       <c r="EC17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED17" t="n">
         <v>0</v>
@@ -9939,52 +9939,52 @@
         <v>-0</v>
       </c>
       <c r="EF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG17" t="n">
-        <v>-0.06443397773357702</v>
+        <v>-0.06448685242536123</v>
       </c>
       <c r="EH17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.04910726375138526</v>
+        <v>0.04072957222628407</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.05981168490956734</v>
+        <v>0.03357087421697454</v>
       </c>
       <c r="EK17" t="n">
         <v>-0</v>
       </c>
       <c r="EL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN17" t="n">
         <v>-0</v>
       </c>
       <c r="EO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP17" t="n">
-        <v>-0.09765223696534031</v>
+        <v>-0.03098754390562455</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.01297594609792058</v>
+        <v>0.03718359584312891</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.03246185574200013</v>
+        <v>-0.02541617963634189</v>
       </c>
       <c r="ET17" t="n">
         <v>-0</v>
       </c>
       <c r="EU17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV17" t="n">
         <v>0</v>
@@ -9993,49 +9993,49 @@
         <v>-0</v>
       </c>
       <c r="EX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY17" t="n">
-        <v>-0.1067308653085313</v>
+        <v>-0.1059203220669601</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.04758604989390637</v>
+        <v>0.08954067017227244</v>
       </c>
       <c r="FB17" t="n">
-        <v>-0.01753207852277998</v>
+        <v>-0.002131775715749209</v>
       </c>
       <c r="FC17" t="n">
         <v>-0</v>
       </c>
       <c r="FD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE17" t="n">
         <v>0</v>
       </c>
       <c r="FF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG17" t="n">
         <v>-0</v>
       </c>
       <c r="FH17" t="n">
-        <v>-0.008516428262184442</v>
+        <v>-0.07387302271480946</v>
       </c>
       <c r="FI17" t="n">
         <v>-0</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.08237470908389527</v>
+        <v>0.06860750375498634</v>
       </c>
       <c r="FK17" t="n">
-        <v>-0.05888569332431867</v>
+        <v>0.02282503715223478</v>
       </c>
       <c r="FL17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM17" t="n">
         <v>0</v>
@@ -10044,22 +10044,22 @@
         <v>0</v>
       </c>
       <c r="FO17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP17" t="n">
         <v>-0</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.005152086651182204</v>
+        <v>0.002290268469196891</v>
       </c>
       <c r="FR17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.04180963442262309</v>
+        <v>0.04023216929595631</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.01510544244090657</v>
+        <v>-0.01302325111248717</v>
       </c>
       <c r="FU17" t="n">
         <v>-0</v>
@@ -10068,37 +10068,37 @@
         <v>-0</v>
       </c>
       <c r="FW17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ17" t="n">
-        <v>-0.01912076430437615</v>
+        <v>-0.09381738614554556</v>
       </c>
       <c r="GA17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB17" t="n">
-        <v>-0.06579304403724877</v>
+        <v>0.02625538585077087</v>
       </c>
       <c r="GC17" t="n">
         <v>0</v>
       </c>
       <c r="GD17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE17" t="n">
         <v>-0</v>
       </c>
       <c r="GF17" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG17" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -10106,19 +10106,19 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>0.1648547508579599</v>
+        <v>0.2341918404574676</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.02504745612561559</v>
+        <v>0.01315812594329701</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.09980793675935282</v>
+        <v>-0.1025450553061346</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -10133,73 +10133,73 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1218032666757083</v>
+        <v>0.320709940465288</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.02637892129682433</v>
+        <v>-0.05120694675259566</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.115123146069682</v>
+        <v>-0.09399224503140993</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>-0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.02758037504679387</v>
+        <v>0.07772921439826226</v>
       </c>
       <c r="U18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.005139392661680093</v>
+        <v>-0.04124570987875489</v>
       </c>
       <c r="X18" t="n">
-        <v>0.009331709342214218</v>
+        <v>0.002159418473651942</v>
       </c>
       <c r="Y18" t="n">
         <v>-0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB18" t="n">
         <v>-0</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.02088900012172525</v>
+        <v>-0.007219925699135474</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.0155026206288224</v>
+        <v>-0.08771169068742354</v>
       </c>
       <c r="AG18" t="n">
-        <v>-0.001949717538437804</v>
+        <v>-0.02342431905905968</v>
       </c>
       <c r="AH18" t="n">
         <v>-0</v>
@@ -10208,28 +10208,28 @@
         <v>-0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.01453777702843856</v>
+        <v>0.05222001594783877</v>
       </c>
       <c r="AM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>-0.02165796581868184</v>
+        <v>0.0005845635737837538</v>
       </c>
       <c r="AP18" t="n">
-        <v>-0.02364366689883068</v>
+        <v>-0.01722361717815129</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR18" t="n">
         <v>-0</v>
@@ -10238,28 +10238,28 @@
         <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.1209478962685901</v>
+        <v>0.2701445644035002</v>
       </c>
       <c r="AV18" t="n">
         <v>-0</v>
       </c>
       <c r="AW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>-0.02231046641938418</v>
+        <v>-0.102573914628523</v>
       </c>
       <c r="AY18" t="n">
-        <v>-0.0470718711704563</v>
+        <v>-0.05291778991652948</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
         <v>0</v>
@@ -10268,61 +10268,61 @@
         <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>0.04445688442482117</v>
+        <v>0.01845668200888299</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF18" t="n">
         <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>-0.03307847963843713</v>
+        <v>-0.04078249510629325</v>
       </c>
       <c r="BH18" t="n">
-        <v>-0.04027577864932401</v>
+        <v>-0.05325865383400846</v>
       </c>
       <c r="BI18" t="n">
         <v>0</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.05352565533037628</v>
+        <v>0.03347790115318051</v>
       </c>
       <c r="BN18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP18" t="n">
-        <v>0.02987102406762041</v>
+        <v>0.04302448815901352</v>
       </c>
       <c r="BQ18" t="n">
-        <v>0.01015372692198228</v>
+        <v>-0.006004380808839641</v>
       </c>
       <c r="BR18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU18" t="n">
         <v>-0</v>
       </c>
       <c r="BV18" t="n">
-        <v>0.05462192430735969</v>
+        <v>0.2006072752635308</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
@@ -10331,10 +10331,10 @@
         <v>0</v>
       </c>
       <c r="BY18" t="n">
-        <v>-0.001987957499832462</v>
+        <v>-0.02180503907511559</v>
       </c>
       <c r="BZ18" t="n">
-        <v>-0.02287038738643813</v>
+        <v>-0.03890084035720644</v>
       </c>
       <c r="CA18" t="n">
         <v>-0</v>
@@ -10349,19 +10349,19 @@
         <v>-0</v>
       </c>
       <c r="CE18" t="n">
-        <v>-0.03095794874173191</v>
+        <v>-0.06982227152944853</v>
       </c>
       <c r="CF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG18" t="n">
         <v>-0</v>
       </c>
       <c r="CH18" t="n">
-        <v>-0.00350763227703766</v>
+        <v>0.00416742866064286</v>
       </c>
       <c r="CI18" t="n">
-        <v>0.02881647898612778</v>
+        <v>0.04150079091136571</v>
       </c>
       <c r="CJ18" t="n">
         <v>0</v>
@@ -10370,52 +10370,52 @@
         <v>0</v>
       </c>
       <c r="CL18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN18" t="n">
-        <v>-0.01902584167142009</v>
+        <v>-0.1539450702271512</v>
       </c>
       <c r="CO18" t="n">
         <v>-0</v>
       </c>
       <c r="CP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ18" t="n">
-        <v>0.003492728126000542</v>
+        <v>0.08496192506582732</v>
       </c>
       <c r="CR18" t="n">
-        <v>-0.01409466348839713</v>
+        <v>0.04041863654870051</v>
       </c>
       <c r="CS18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT18" t="n">
         <v>-0</v>
       </c>
       <c r="CU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW18" t="n">
-        <v>-0.02193938402592312</v>
+        <v>-0.07103513136780479</v>
       </c>
       <c r="CX18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY18" t="n">
         <v>0</v>
       </c>
       <c r="CZ18" t="n">
-        <v>-0.003514967237797089</v>
+        <v>-0.007296164809262333</v>
       </c>
       <c r="DA18" t="n">
-        <v>0.02928863795551232</v>
+        <v>0.05184995136861095</v>
       </c>
       <c r="DB18" t="n">
         <v>0</v>
@@ -10427,22 +10427,22 @@
         <v>0</v>
       </c>
       <c r="DE18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF18" t="n">
-        <v>-0.02760217247733659</v>
+        <v>-0.05815483838410096</v>
       </c>
       <c r="DG18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.01183416086500884</v>
+        <v>-0.1029218440919842</v>
       </c>
       <c r="DJ18" t="n">
-        <v>-0.001087937006004867</v>
+        <v>0.01317833659910127</v>
       </c>
       <c r="DK18" t="n">
         <v>0</v>
@@ -10451,52 +10451,52 @@
         <v>-0</v>
       </c>
       <c r="DM18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN18" t="n">
         <v>-0</v>
       </c>
       <c r="DO18" t="n">
-        <v>-0.01842710889499481</v>
+        <v>-0.07256245606367435</v>
       </c>
       <c r="DP18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR18" t="n">
-        <v>0.01299350996236149</v>
+        <v>0.05889103472642463</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.007493966803830719</v>
+        <v>-0.0355547537313828</v>
       </c>
       <c r="DT18" t="n">
         <v>0</v>
       </c>
       <c r="DU18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW18" t="n">
         <v>-0</v>
       </c>
       <c r="DX18" t="n">
-        <v>0.01832201683221936</v>
+        <v>0.001830395391236953</v>
       </c>
       <c r="DY18" t="n">
         <v>0</v>
       </c>
       <c r="DZ18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA18" t="n">
-        <v>-0.01108798249278215</v>
+        <v>0.1149820344243987</v>
       </c>
       <c r="EB18" t="n">
-        <v>-0.0235302679594132</v>
+        <v>-0.09240178925817219</v>
       </c>
       <c r="EC18" t="n">
         <v>-0</v>
@@ -10511,7 +10511,7 @@
         <v>-0</v>
       </c>
       <c r="EG18" t="n">
-        <v>-0.01499631304029879</v>
+        <v>0.006147978094321366</v>
       </c>
       <c r="EH18" t="n">
         <v>-0</v>
@@ -10520,37 +10520,37 @@
         <v>0</v>
       </c>
       <c r="EJ18" t="n">
-        <v>0.001400817095536431</v>
+        <v>-0.03753543421538768</v>
       </c>
       <c r="EK18" t="n">
-        <v>0.01809802187962909</v>
+        <v>0.01229141933733305</v>
       </c>
       <c r="EL18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM18" t="n">
         <v>-0</v>
       </c>
       <c r="EN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP18" t="n">
-        <v>-0.007650833348380848</v>
+        <v>0.01011593180673912</v>
       </c>
       <c r="EQ18" t="n">
         <v>0</v>
       </c>
       <c r="ER18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES18" t="n">
-        <v>-0.001646841414541164</v>
+        <v>-0.07181351046474277</v>
       </c>
       <c r="ET18" t="n">
-        <v>0.009503531397023417</v>
+        <v>0.04844321994538853</v>
       </c>
       <c r="EU18" t="n">
         <v>-0</v>
@@ -10559,106 +10559,106 @@
         <v>0</v>
       </c>
       <c r="EW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX18" t="n">
         <v>-0</v>
       </c>
       <c r="EY18" t="n">
-        <v>-0.0220206234384204</v>
+        <v>-0.08129701582299353</v>
       </c>
       <c r="EZ18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB18" t="n">
-        <v>-0.002567585095063978</v>
+        <v>-0.01603487987638173</v>
       </c>
       <c r="FC18" t="n">
-        <v>0.03144854608505167</v>
+        <v>0.04379914009190258</v>
       </c>
       <c r="FD18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE18" t="n">
         <v>0</v>
       </c>
       <c r="FF18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG18" t="n">
         <v>0</v>
       </c>
       <c r="FH18" t="n">
-        <v>-0.003562778845847517</v>
+        <v>-0.1197199047164846</v>
       </c>
       <c r="FI18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ18" t="n">
         <v>-0</v>
       </c>
       <c r="FK18" t="n">
-        <v>-0.02660959030683362</v>
+        <v>0.0995169271998825</v>
       </c>
       <c r="FL18" t="n">
-        <v>0.02488616460940636</v>
+        <v>0.03676429023320091</v>
       </c>
       <c r="FM18" t="n">
         <v>0</v>
       </c>
       <c r="FN18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP18" t="n">
         <v>-0</v>
       </c>
       <c r="FQ18" t="n">
-        <v>0.000127835752165547</v>
+        <v>5.387835924112435e-05</v>
       </c>
       <c r="FR18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS18" t="n">
         <v>-0</v>
       </c>
       <c r="FT18" t="n">
-        <v>-0.001704778038144577</v>
+        <v>-0.004341473189697439</v>
       </c>
       <c r="FU18" t="n">
-        <v>0.02200386947344418</v>
+        <v>-0.05365014326326422</v>
       </c>
       <c r="FV18" t="n">
         <v>-0</v>
       </c>
       <c r="FW18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ18" t="n">
-        <v>-0.01306653279083216</v>
+        <v>0.001893361423807019</v>
       </c>
       <c r="GA18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB18" t="n">
         <v>-0</v>
       </c>
       <c r="GC18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD18" t="n">
-        <v>-0.02317327475146633</v>
+        <v>0.01098947252862338</v>
       </c>
       <c r="GE18" t="n">
         <v>-0</v>
@@ -10667,7 +10667,7 @@
         <v>-0</v>
       </c>
       <c r="GG18" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -10675,16 +10675,16 @@
         <v>0</v>
       </c>
       <c r="B19" t="n">
-        <v>0.7978415186850903</v>
+        <v>0.5552409609340624</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3724168888663222</v>
+        <v>-0.2902661187759338</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2508841338645919</v>
+        <v>-0.1082477963748972</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -10699,19 +10699,19 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5588645833494585</v>
+        <v>0.5779520339815297</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.3238074279766862</v>
+        <v>-0.3796980322574373</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.266819701974769</v>
+        <v>-0.1892884819676545</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -10729,70 +10729,70 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1776504019487528</v>
+        <v>0.09298251216937455</v>
       </c>
       <c r="U19" t="n">
         <v>-0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.06216632050375315</v>
+        <v>-0.09472142859953087</v>
       </c>
       <c r="W19" t="n">
-        <v>0.05815072403019913</v>
+        <v>-0.1117991818319842</v>
       </c>
       <c r="X19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>-0</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.09866186530625627</v>
+        <v>-0.04880841412273557</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0.01213064031219623</v>
+        <v>-0.1162611566058305</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.007948331998843901</v>
+        <v>-0.1176263409512254</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.05911898324733725</v>
+        <v>0.2086284942103807</v>
       </c>
       <c r="AM19" t="n">
         <v>-0</v>
       </c>
       <c r="AN19" t="n">
-        <v>-0.0637496102554674</v>
+        <v>-0.1032486737963238</v>
       </c>
       <c r="AO19" t="n">
-        <v>-0.08930550502377439</v>
+        <v>0.07452272600897449</v>
       </c>
       <c r="AP19" t="n">
         <v>0</v>
@@ -10810,25 +10810,25 @@
         <v>-0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.6381122171090792</v>
+        <v>0.5724225808191926</v>
       </c>
       <c r="AV19" t="n">
         <v>-0</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.01834428267234666</v>
+        <v>-0.1280569947390052</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.0351731341726736</v>
+        <v>-0.2683799807627367</v>
       </c>
       <c r="AY19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
         <v>-0</v>
@@ -10837,16 +10837,16 @@
         <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>0.0781083304154581</v>
+        <v>-0.06818535951500193</v>
       </c>
       <c r="BE19" t="n">
         <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>-0.1719955078945217</v>
+        <v>-0.07819765597724797</v>
       </c>
       <c r="BG19" t="n">
-        <v>-0.2885983605458074</v>
+        <v>-0.04699246247838873</v>
       </c>
       <c r="BH19" t="n">
         <v>0</v>
@@ -10855,7 +10855,7 @@
         <v>-0</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK19" t="n">
         <v>0</v>
@@ -10864,22 +10864,22 @@
         <v>-0</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.1834078068854868</v>
+        <v>0.01291119282318859</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.03322645080665308</v>
+        <v>0.01859459316334057</v>
       </c>
       <c r="BP19" t="n">
-        <v>0.1708416765224476</v>
+        <v>0.1199914088679753</v>
       </c>
       <c r="BQ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS19" t="n">
         <v>-0</v>
@@ -10888,28 +10888,28 @@
         <v>-0</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.3205092544136792</v>
+        <v>0.3873165235218122</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX19" t="n">
-        <v>0.01592150635246711</v>
+        <v>-0.164779120551717</v>
       </c>
       <c r="BY19" t="n">
-        <v>0.053266713924842</v>
+        <v>-0.09238008504509268</v>
       </c>
       <c r="BZ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA19" t="n">
         <v>-0</v>
       </c>
       <c r="CB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC19" t="n">
         <v>0</v>
@@ -10918,16 +10918,16 @@
         <v>-0</v>
       </c>
       <c r="CE19" t="n">
-        <v>-0.1503378435562021</v>
+        <v>-0.1891706045669509</v>
       </c>
       <c r="CF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG19" t="n">
-        <v>0.04203984291797382</v>
+        <v>0.1213241138383741</v>
       </c>
       <c r="CH19" t="n">
-        <v>-0.008256277851588558</v>
+        <v>0.04490953125038452</v>
       </c>
       <c r="CI19" t="n">
         <v>-0</v>
@@ -10939,25 +10939,25 @@
         <v>0</v>
       </c>
       <c r="CL19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM19" t="n">
         <v>0</v>
       </c>
       <c r="CN19" t="n">
-        <v>-0.04415709420683111</v>
+        <v>-0.2449213929335576</v>
       </c>
       <c r="CO19" t="n">
         <v>-0</v>
       </c>
       <c r="CP19" t="n">
-        <v>-0.1594884280342066</v>
+        <v>0.2808166904271556</v>
       </c>
       <c r="CQ19" t="n">
-        <v>-0.1183346760407576</v>
+        <v>0.1343012562919133</v>
       </c>
       <c r="CR19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS19" t="n">
         <v>-0</v>
@@ -10966,22 +10966,22 @@
         <v>-0</v>
       </c>
       <c r="CU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW19" t="n">
-        <v>-0.1152719528799426</v>
+        <v>-0.1751759653671641</v>
       </c>
       <c r="CX19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY19" t="n">
-        <v>0.07222800225322808</v>
+        <v>0.1454934190027378</v>
       </c>
       <c r="CZ19" t="n">
-        <v>-0.01806541221982782</v>
+        <v>0.03723042610935302</v>
       </c>
       <c r="DA19" t="n">
         <v>0</v>
@@ -10999,22 +10999,22 @@
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>-0.09831606243743513</v>
+        <v>-0.1255264793527658</v>
       </c>
       <c r="DG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH19" t="n">
-        <v>0.07142133219262224</v>
+        <v>0.03279971313395349</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.007084754453326545</v>
+        <v>-0.08196385155659551</v>
       </c>
       <c r="DJ19" t="n">
         <v>-0</v>
       </c>
       <c r="DK19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL19" t="n">
         <v>0</v>
@@ -11026,19 +11026,19 @@
         <v>-0</v>
       </c>
       <c r="DO19" t="n">
-        <v>-0.0882540843277225</v>
+        <v>-0.08310290709037248</v>
       </c>
       <c r="DP19" t="n">
         <v>0</v>
       </c>
       <c r="DQ19" t="n">
-        <v>0.01403656102374398</v>
+        <v>-0.03318104804058379</v>
       </c>
       <c r="DR19" t="n">
-        <v>-0.07036151703968796</v>
+        <v>-0.02212896388121526</v>
       </c>
       <c r="DS19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT19" t="n">
         <v>-0</v>
@@ -11053,52 +11053,52 @@
         <v>-0</v>
       </c>
       <c r="DX19" t="n">
-        <v>0.02493202216406493</v>
+        <v>0.1590321923096618</v>
       </c>
       <c r="DY19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ19" t="n">
-        <v>0.003699599308578088</v>
+        <v>0.09167235018732746</v>
       </c>
       <c r="EA19" t="n">
-        <v>-0.08131490290132107</v>
+        <v>-0.06407103582599656</v>
       </c>
       <c r="EB19" t="n">
         <v>0</v>
       </c>
       <c r="EC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED19" t="n">
         <v>0</v>
       </c>
       <c r="EE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF19" t="n">
         <v>0</v>
       </c>
       <c r="EG19" t="n">
-        <v>-0.1177391621151128</v>
+        <v>-0.1117126035588136</v>
       </c>
       <c r="EH19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI19" t="n">
-        <v>0.03901162760285022</v>
+        <v>0.07676916672651418</v>
       </c>
       <c r="EJ19" t="n">
-        <v>0.1166130370397863</v>
+        <v>0.08225096807016141</v>
       </c>
       <c r="EK19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL19" t="n">
         <v>-0</v>
       </c>
       <c r="EM19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN19" t="n">
         <v>-0</v>
@@ -11107,22 +11107,22 @@
         <v>0</v>
       </c>
       <c r="EP19" t="n">
-        <v>-0.06642034725194329</v>
+        <v>-0.06075098886903216</v>
       </c>
       <c r="EQ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER19" t="n">
-        <v>0.05108335644064613</v>
+        <v>0.09338915539928097</v>
       </c>
       <c r="ES19" t="n">
-        <v>0.02178091909487521</v>
+        <v>-0.0805075252263233</v>
       </c>
       <c r="ET19" t="n">
         <v>-0</v>
       </c>
       <c r="EU19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV19" t="n">
         <v>0</v>
@@ -11131,46 +11131,46 @@
         <v>-0</v>
       </c>
       <c r="EX19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY19" t="n">
-        <v>-0.1148514425409304</v>
+        <v>-0.208442676571879</v>
       </c>
       <c r="EZ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA19" t="n">
-        <v>0.05855926171792433</v>
+        <v>0.1500402228765634</v>
       </c>
       <c r="FB19" t="n">
-        <v>0.01348519702921554</v>
+        <v>0.02132321514782566</v>
       </c>
       <c r="FC19" t="n">
         <v>-0</v>
       </c>
       <c r="FD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE19" t="n">
         <v>0</v>
       </c>
       <c r="FF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG19" t="n">
         <v>0</v>
       </c>
       <c r="FH19" t="n">
-        <v>-0.02122266028565106</v>
+        <v>-0.06963544662572525</v>
       </c>
       <c r="FI19" t="n">
         <v>-0</v>
       </c>
       <c r="FJ19" t="n">
-        <v>0.08262858338831688</v>
+        <v>0.09752360109633855</v>
       </c>
       <c r="FK19" t="n">
-        <v>-0.08717098396497903</v>
+        <v>0.022152912875984</v>
       </c>
       <c r="FL19" t="n">
         <v>-0</v>
@@ -11182,22 +11182,22 @@
         <v>-0</v>
       </c>
       <c r="FO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ19" t="n">
-        <v>-0.0004744326762285435</v>
+        <v>0.0007335533711449042</v>
       </c>
       <c r="FR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS19" t="n">
-        <v>0.01221328547809513</v>
+        <v>0.1041004202152458</v>
       </c>
       <c r="FT19" t="n">
-        <v>-0.002093466770778301</v>
+        <v>-0.006868634613739278</v>
       </c>
       <c r="FU19" t="n">
         <v>-0</v>
@@ -11212,28 +11212,28 @@
         <v>0</v>
       </c>
       <c r="FY19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ19" t="n">
-        <v>0.02425690891282445</v>
+        <v>-0.166065060759624</v>
       </c>
       <c r="GA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB19" t="n">
-        <v>-0.05086954430570374</v>
+        <v>0.1031712785589519</v>
       </c>
       <c r="GC19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE19" t="n">
         <v>-0</v>
       </c>
       <c r="GF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG19" t="n">
         <v>-0</v>
@@ -11244,22 +11244,22 @@
         <v>0</v>
       </c>
       <c r="B20" t="n">
-        <v>0.2407201062960056</v>
+        <v>0.2781248725477181</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1001316642488077</v>
+        <v>0.04581605353131121</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1031722245071023</v>
+        <v>-0.185978997686482</v>
       </c>
       <c r="G20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>-0</v>
@@ -11271,7 +11271,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1730484188565886</v>
+        <v>0.4287557030665199</v>
       </c>
       <c r="L20" t="n">
         <v>-0</v>
@@ -11280,16 +11280,16 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1009049178685952</v>
+        <v>-0.05812045636473664</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1355064624039245</v>
+        <v>-0.1734399278378497</v>
       </c>
       <c r="P20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -11298,7 +11298,7 @@
         <v>-0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.04427735668933982</v>
+        <v>0.08884269509769815</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -11307,16 +11307,16 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.01231683872242837</v>
+        <v>-0.05601502494857348</v>
       </c>
       <c r="X20" t="n">
-        <v>0.01808159399229478</v>
+        <v>-0.00538673692549281</v>
       </c>
       <c r="Y20" t="n">
         <v>-0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -11325,34 +11325,34 @@
         <v>-0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.04526230826904762</v>
+        <v>-0.01228129726677036</v>
       </c>
       <c r="AD20" t="n">
         <v>-0</v>
       </c>
       <c r="AE20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>0.02658908413001799</v>
+        <v>-0.1539140460794433</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.00364037996117704</v>
+        <v>-0.07411207849082282</v>
       </c>
       <c r="AH20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>-0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.04285036490212545</v>
+        <v>0.03630132501764195</v>
       </c>
       <c r="AM20" t="n">
         <v>0</v>
@@ -11361,13 +11361,13 @@
         <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>-0.008040848478472284</v>
+        <v>-0.03718557212550315</v>
       </c>
       <c r="AP20" t="n">
-        <v>-0.02995096628865895</v>
+        <v>-0.1034128899989514</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR20" t="n">
         <v>-0</v>
@@ -11376,55 +11376,55 @@
         <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.1799854417911867</v>
+        <v>0.3859212428423268</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW20" t="n">
         <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>-0.03839409383958001</v>
+        <v>-0.1212166410074029</v>
       </c>
       <c r="AY20" t="n">
-        <v>-0.06647560297271633</v>
+        <v>-0.1125602232418541</v>
       </c>
       <c r="AZ20" t="n">
         <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD20" t="n">
-        <v>0.03828592635063219</v>
+        <v>-0.0252646766413776</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF20" t="n">
         <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>-0.0906922589565257</v>
+        <v>-0.04945958420223942</v>
       </c>
       <c r="BH20" t="n">
-        <v>-0.02124476160391486</v>
+        <v>-0.1198410587833397</v>
       </c>
       <c r="BI20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK20" t="n">
         <v>0</v>
@@ -11433,46 +11433,46 @@
         <v>-0</v>
       </c>
       <c r="BM20" t="n">
-        <v>0.0533377734633249</v>
+        <v>0.09817316103684719</v>
       </c>
       <c r="BN20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO20" t="n">
         <v>-0</v>
       </c>
       <c r="BP20" t="n">
-        <v>0.0267745062678273</v>
+        <v>0.119433296919838</v>
       </c>
       <c r="BQ20" t="n">
-        <v>0.02983262693447337</v>
+        <v>0.0007031888518522945</v>
       </c>
       <c r="BR20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS20" t="n">
         <v>0</v>
       </c>
       <c r="BT20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV20" t="n">
-        <v>0.09246692008934611</v>
+        <v>0.2180563456015543</v>
       </c>
       <c r="BW20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX20" t="n">
         <v>0</v>
       </c>
       <c r="BY20" t="n">
-        <v>-0.02646206250306124</v>
+        <v>-0.06086127732215943</v>
       </c>
       <c r="BZ20" t="n">
-        <v>-0.02663326664090784</v>
+        <v>-0.08953303753772011</v>
       </c>
       <c r="CA20" t="n">
         <v>-0</v>
@@ -11484,79 +11484,79 @@
         <v>0</v>
       </c>
       <c r="CD20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE20" t="n">
-        <v>-0.0374517850860395</v>
+        <v>-0.09145895581442655</v>
       </c>
       <c r="CF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG20" t="n">
         <v>-0</v>
       </c>
       <c r="CH20" t="n">
-        <v>-0.001947914419154535</v>
+        <v>0.04252067544880964</v>
       </c>
       <c r="CI20" t="n">
-        <v>0.02905664623759373</v>
+        <v>0.08551134227558271</v>
       </c>
       <c r="CJ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK20" t="n">
         <v>0</v>
       </c>
       <c r="CL20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM20" t="n">
         <v>0</v>
       </c>
       <c r="CN20" t="n">
-        <v>-0.02186202412132768</v>
+        <v>-0.2407562508950992</v>
       </c>
       <c r="CO20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ20" t="n">
-        <v>-0.008828124125590919</v>
+        <v>0.1836635003516358</v>
       </c>
       <c r="CR20" t="n">
-        <v>-0.01260897992107452</v>
+        <v>0.1551424316972161</v>
       </c>
       <c r="CS20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT20" t="n">
         <v>-0</v>
       </c>
       <c r="CU20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW20" t="n">
-        <v>-0.02841496609545813</v>
+        <v>-0.09619234002500157</v>
       </c>
       <c r="CX20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY20" t="n">
         <v>0</v>
       </c>
       <c r="CZ20" t="n">
-        <v>-0.002074283367422653</v>
+        <v>0.004590121584978706</v>
       </c>
       <c r="DA20" t="n">
-        <v>0.03400347324673296</v>
+        <v>0.0778180715101084</v>
       </c>
       <c r="DB20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC20" t="n">
         <v>-0</v>
@@ -11565,79 +11565,79 @@
         <v>0</v>
       </c>
       <c r="DE20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF20" t="n">
-        <v>-0.01153155658877082</v>
+        <v>-0.02444859879323869</v>
       </c>
       <c r="DG20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI20" t="n">
-        <v>-0.003214535805851605</v>
+        <v>-0.1026470132698666</v>
       </c>
       <c r="DJ20" t="n">
-        <v>-0.006210866451173284</v>
+        <v>-0.006412993794824772</v>
       </c>
       <c r="DK20" t="n">
         <v>0</v>
       </c>
       <c r="DL20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO20" t="n">
-        <v>0.00304471626921749</v>
+        <v>-0.02394679820436801</v>
       </c>
       <c r="DP20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR20" t="n">
-        <v>0.01299123473793178</v>
+        <v>0.0341249005984746</v>
       </c>
       <c r="DS20" t="n">
-        <v>0.03077977812592936</v>
+        <v>-0.01184630834894415</v>
       </c>
       <c r="DT20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU20" t="n">
         <v>-0</v>
       </c>
       <c r="DV20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW20" t="n">
         <v>-0</v>
       </c>
       <c r="DX20" t="n">
-        <v>0.01306581392894241</v>
+        <v>0.04982916764105679</v>
       </c>
       <c r="DY20" t="n">
         <v>0</v>
       </c>
       <c r="DZ20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA20" t="n">
-        <v>-0.01514560790655107</v>
+        <v>0.02129258344574008</v>
       </c>
       <c r="EB20" t="n">
-        <v>-0.003922630817114065</v>
+        <v>0.02387380002030011</v>
       </c>
       <c r="EC20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED20" t="n">
         <v>0</v>
@@ -11646,22 +11646,22 @@
         <v>-0</v>
       </c>
       <c r="EF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG20" t="n">
-        <v>-0.0270905956935159</v>
+        <v>-0.009549061297533688</v>
       </c>
       <c r="EH20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI20" t="n">
         <v>0</v>
       </c>
       <c r="EJ20" t="n">
-        <v>0.01072362952028961</v>
+        <v>-0.0525300458747209</v>
       </c>
       <c r="EK20" t="n">
-        <v>0.01633719072287009</v>
+        <v>0.0414617748642514</v>
       </c>
       <c r="EL20" t="n">
         <v>-0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="EO20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP20" t="n">
-        <v>-0.01100286788433712</v>
+        <v>-0.005099767539972115</v>
       </c>
       <c r="EQ20" t="n">
         <v>0</v>
@@ -11685,91 +11685,91 @@
         <v>-0</v>
       </c>
       <c r="ES20" t="n">
-        <v>-0.01521126547827673</v>
+        <v>-0.04670959256063017</v>
       </c>
       <c r="ET20" t="n">
-        <v>0.02273794677330662</v>
+        <v>0.0472165913474697</v>
       </c>
       <c r="EU20" t="n">
         <v>-0</v>
       </c>
       <c r="EV20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY20" t="n">
-        <v>-0.02777054832036599</v>
+        <v>-0.1008448789929375</v>
       </c>
       <c r="EZ20" t="n">
         <v>0</v>
       </c>
       <c r="FA20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB20" t="n">
-        <v>-0.004986344803404904</v>
+        <v>-0.001579343701588003</v>
       </c>
       <c r="FC20" t="n">
-        <v>0.03192235228520635</v>
+        <v>0.07137323582837361</v>
       </c>
       <c r="FD20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE20" t="n">
         <v>0</v>
       </c>
       <c r="FF20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH20" t="n">
-        <v>-0.03112342522913756</v>
+        <v>-0.125913350952364</v>
       </c>
       <c r="FI20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ20" t="n">
         <v>-0</v>
       </c>
       <c r="FK20" t="n">
-        <v>-0.0251443624022482</v>
+        <v>0.0976036218795759</v>
       </c>
       <c r="FL20" t="n">
-        <v>-0.02554352250148055</v>
+        <v>-0.1387085400731413</v>
       </c>
       <c r="FM20" t="n">
         <v>0</v>
       </c>
       <c r="FN20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO20" t="n">
         <v>0</v>
       </c>
       <c r="FP20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ20" t="n">
-        <v>-0.005445979959760368</v>
+        <v>-0.02061030386757668</v>
       </c>
       <c r="FR20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS20" t="n">
         <v>-0</v>
       </c>
       <c r="FT20" t="n">
-        <v>-0.0001971430753856063</v>
+        <v>0.0001621761754784913</v>
       </c>
       <c r="FU20" t="n">
-        <v>0.02065878746002074</v>
+        <v>0.06688238872280466</v>
       </c>
       <c r="FV20" t="n">
         <v>-0</v>
@@ -11778,34 +11778,34 @@
         <v>0</v>
       </c>
       <c r="FX20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ20" t="n">
-        <v>-0.006994639013094071</v>
+        <v>-0.0206466253895013</v>
       </c>
       <c r="GA20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB20" t="n">
         <v>-0</v>
       </c>
       <c r="GC20" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD20" t="n">
-        <v>-0.0135381558112911</v>
+        <v>0.003362787191383226</v>
       </c>
       <c r="GE20" t="n">
         <v>-0</v>
       </c>
       <c r="GF20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG20" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
